--- a/0_Document/타워 정보.xlsx
+++ b/0_Document/타워 정보.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Adventure\Assets\0_Adventure\Deploy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Project LinkDeploy\0_Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E09F688-D15B-4483-931D-B981F443C508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B712CC3-09BD-4F54-90E4-668D48E68D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="64">
   <si>
     <t>Type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -39,18 +39,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>FactoryBuff</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Tower</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TowerBuff</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -63,10 +55,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>타워 공격력 증가량(타워 버프만)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Slingshot</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -111,10 +99,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>생산 증가량(공장 버프만)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>쇠</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -255,14 +239,6 @@
   </si>
   <si>
     <t>냉기 제련소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공장 가속소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>타워 강화소</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -345,9 +321,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -628,7 +603,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
@@ -646,16 +621,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" t="s">
         <v>28</v>
-      </c>
-      <c r="J1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -666,44 +641,44 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>10</v>
@@ -711,22 +686,22 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E5">
         <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G5">
         <v>10</v>
@@ -734,10 +709,10 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I7" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -745,31 +720,31 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
         <v>48</v>
       </c>
-      <c r="C8" t="s">
-        <v>52</v>
-      </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G8">
         <v>5</v>
       </c>
       <c r="H8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I8">
         <v>5</v>
       </c>
       <c r="J8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -777,31 +752,31 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G9">
         <v>5</v>
       </c>
       <c r="H9" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I9">
         <v>5</v>
       </c>
       <c r="J9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -809,31 +784,31 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>5</v>
       </c>
       <c r="H10" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I10">
         <v>5</v>
       </c>
       <c r="J10" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -841,246 +816,202 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G11">
         <v>5</v>
       </c>
       <c r="H11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I11">
         <v>5</v>
       </c>
       <c r="J11" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H13" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="I13">
         <v>5</v>
       </c>
       <c r="J13" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" t="s">
         <v>41</v>
-      </c>
-      <c r="C14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" t="s">
-        <v>45</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H14" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="I14">
         <v>5</v>
       </c>
       <c r="J14" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E16" t="s">
         <v>21</v>
       </c>
+      <c r="F16" t="s">
+        <v>27</v>
+      </c>
+      <c r="G16" t="s">
+        <v>6</v>
+      </c>
+      <c r="H16" t="s">
+        <v>23</v>
+      </c>
+      <c r="I16" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>3</v>
       </c>
       <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17">
+        <v>6</v>
+      </c>
+      <c r="F17">
+        <v>0.7</v>
+      </c>
+      <c r="G17">
+        <v>50</v>
+      </c>
+      <c r="H17">
         <v>3</v>
       </c>
-      <c r="C17" t="s">
-        <v>58</v>
-      </c>
-      <c r="D17" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17" s="1">
-        <v>1</v>
+      <c r="I17" t="s">
+        <v>19</v>
+      </c>
+      <c r="J17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18">
+        <v>10</v>
+      </c>
+      <c r="F18">
+        <v>1.2</v>
+      </c>
+      <c r="G18">
+        <v>35</v>
+      </c>
+      <c r="H18">
+        <v>5</v>
+      </c>
+      <c r="I18" t="s">
+        <v>10</v>
+      </c>
+      <c r="J18" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E20" s="1">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" t="s">
-        <v>31</v>
-      </c>
-      <c r="G23" t="s">
-        <v>8</v>
-      </c>
-      <c r="H23" t="s">
-        <v>27</v>
-      </c>
-      <c r="I23" t="s">
+      <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19">
+        <v>15</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19">
+        <v>50</v>
+      </c>
+      <c r="H19">
+        <v>10</v>
+      </c>
+      <c r="I19" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" t="s">
-        <v>30</v>
-      </c>
-      <c r="E24">
-        <v>6</v>
-      </c>
-      <c r="F24">
-        <v>0.7</v>
-      </c>
-      <c r="G24">
-        <v>50</v>
-      </c>
-      <c r="H24">
-        <v>3</v>
-      </c>
-      <c r="I24" t="s">
-        <v>23</v>
-      </c>
-      <c r="J24" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" t="s">
-        <v>61</v>
-      </c>
-      <c r="D25" t="s">
-        <v>30</v>
-      </c>
-      <c r="E25">
-        <v>10</v>
-      </c>
-      <c r="F25">
-        <v>1.2</v>
-      </c>
-      <c r="G25">
-        <v>35</v>
-      </c>
-      <c r="H25">
-        <v>5</v>
-      </c>
-      <c r="I25" t="s">
-        <v>13</v>
-      </c>
-      <c r="J25" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" t="s">
-        <v>62</v>
-      </c>
-      <c r="D26" t="s">
-        <v>30</v>
-      </c>
-      <c r="E26">
-        <v>15</v>
-      </c>
-      <c r="F26">
-        <v>2</v>
-      </c>
-      <c r="G26">
-        <v>50</v>
-      </c>
-      <c r="H26">
-        <v>10</v>
-      </c>
-      <c r="I26" t="s">
-        <v>14</v>
-      </c>
-      <c r="J26" t="s">
-        <v>38</v>
+      <c r="J19" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/0_Document/타워 정보.xlsx
+++ b/0_Document/타워 정보.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Project LinkDeploy\0_Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B712CC3-09BD-4F54-90E4-668D48E68D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97785456-D2A2-47F5-8F58-3E5A6AAEA01E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="52">
   <si>
     <t>Type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -79,14 +79,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>StoneFactory</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ArrowFactory</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>AmmoFactory</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -127,10 +119,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>마을</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>타워 구역</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -147,14 +135,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>돌을 동그란돌로 만드는 공장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>쇠를 화살로 만드는 공장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>화살, 동그란 돌을 총알로 만드는 공장</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -194,39 +174,11 @@
     <t>방어구역</t>
   </si>
   <si>
-    <t>나무, 쇠</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무와 쇠로 망치를 만드는 공장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HammerFactory</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>망치</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Korea</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>도로</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>망치 공장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>돌 공장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>화살 공장</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -603,7 +555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
@@ -624,13 +576,13 @@
         <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -641,38 +593,38 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E3" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -686,22 +638,22 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E5">
         <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G5">
         <v>10</v>
@@ -709,10 +661,10 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -720,202 +672,170 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>5</v>
       </c>
       <c r="H8" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I8">
         <v>5</v>
       </c>
       <c r="J8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-      <c r="H9" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9">
-        <v>5</v>
-      </c>
-      <c r="J9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-      <c r="H10" t="s">
-        <v>18</v>
-      </c>
-      <c r="I10">
-        <v>5</v>
-      </c>
-      <c r="J10" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="H11" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="I11">
         <v>5</v>
       </c>
       <c r="J11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>58</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" t="s">
         <v>36</v>
       </c>
-      <c r="C13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13">
+      <c r="E12">
         <v>1</v>
       </c>
-      <c r="F13" t="s">
-        <v>60</v>
-      </c>
-      <c r="H13" t="s">
-        <v>57</v>
-      </c>
-      <c r="I13">
+      <c r="F12" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" t="s">
+        <v>45</v>
+      </c>
+      <c r="I12">
         <v>5</v>
       </c>
-      <c r="J13" t="s">
-        <v>39</v>
+      <c r="J12" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>58</v>
-      </c>
-      <c r="B14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
+      <c r="E14" t="s">
+        <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>60</v>
+        <v>24</v>
+      </c>
+      <c r="G14" t="s">
+        <v>6</v>
       </c>
       <c r="H14" t="s">
-        <v>57</v>
-      </c>
-      <c r="I14">
+        <v>21</v>
+      </c>
+      <c r="I14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15">
+        <v>6</v>
+      </c>
+      <c r="F15">
+        <v>0.7</v>
+      </c>
+      <c r="G15">
+        <v>50</v>
+      </c>
+      <c r="H15">
+        <v>3</v>
+      </c>
+      <c r="I15" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" t="s">
         <v>5</v>
       </c>
-      <c r="J14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E16" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" t="s">
-        <v>27</v>
-      </c>
-      <c r="G16" t="s">
-        <v>6</v>
-      </c>
-      <c r="H16" t="s">
+      <c r="C16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" t="s">
         <v>23</v>
       </c>
+      <c r="E16">
+        <v>10</v>
+      </c>
+      <c r="F16">
+        <v>1.2</v>
+      </c>
+      <c r="G16">
+        <v>35</v>
+      </c>
+      <c r="H16">
+        <v>5</v>
+      </c>
       <c r="I16" t="s">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="J16" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -923,95 +843,31 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E17">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F17">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="G17">
         <v>50</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I17" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18">
-        <v>10</v>
-      </c>
-      <c r="F18">
-        <v>1.2</v>
-      </c>
-      <c r="G18">
-        <v>35</v>
-      </c>
-      <c r="H18">
-        <v>5</v>
-      </c>
-      <c r="I18" t="s">
-        <v>10</v>
-      </c>
-      <c r="J18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19">
-        <v>15</v>
-      </c>
-      <c r="F19">
-        <v>2</v>
-      </c>
-      <c r="G19">
-        <v>50</v>
-      </c>
-      <c r="H19">
-        <v>10</v>
-      </c>
-      <c r="I19" t="s">
-        <v>11</v>
-      </c>
-      <c r="J19" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
